--- a/output/laminas_comunales/comunal_o_ocup_a_2020_los_lagos.xlsx
+++ b/output/laminas_comunales/comunal_o_ocup_a_2020_los_lagos.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C211"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -384,37 +384,37 @@
         </is>
       </c>
       <c r="C2">
-        <v>43.5613470786349</v>
+        <v>62.4915353084741</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10208</t>
+          <t>10109</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Quellón</t>
+          <t>Puerto Varas</t>
         </is>
       </c>
       <c r="C3">
-        <v>41.4218755721557</v>
+        <v>59.9249178789301</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>10109</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Puerto Varas</t>
+          <t>Osorno</t>
         </is>
       </c>
       <c r="C4">
-        <v>41.2931971397749</v>
+        <v>59.3002854374525</v>
       </c>
     </row>
     <row r="5">
@@ -429,67 +429,67 @@
         </is>
       </c>
       <c r="C5">
-        <v>39.630191473859</v>
+        <v>59.2498877688446</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10107</t>
+          <t>10208</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Llanquihue</t>
+          <t>Quellón</t>
         </is>
       </c>
       <c r="C6">
-        <v>38.9523256564093</v>
+        <v>57.8652477271126</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10301</t>
+          <t>10204</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Osorno</t>
+          <t>Curaco de Vélez</t>
         </is>
       </c>
       <c r="C7">
-        <v>38.2989173475838</v>
+        <v>57.4271736713364</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10105</t>
+          <t>10107</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Frutillar</t>
+          <t>Llanquihue</t>
         </is>
       </c>
       <c r="C8">
-        <v>36.64247477867</v>
+        <v>56.0806145347834</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10302</t>
+          <t>10307</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Puerto Octay</t>
+          <t>San Pablo</t>
         </is>
       </c>
       <c r="C9">
-        <v>36.6169646432525</v>
+        <v>55.0440528634361</v>
       </c>
     </row>
     <row r="10">
@@ -504,82 +504,82 @@
         </is>
       </c>
       <c r="C10">
-        <v>36.035610664039</v>
+        <v>54.9619482496195</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10102</t>
+          <t>10303</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Calbuco</t>
+          <t>Purranque</t>
         </is>
       </c>
       <c r="C11">
-        <v>34.6602366386631</v>
+        <v>54.889745236566</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10205</t>
+          <t>10105</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Dalcahue</t>
+          <t>Frutillar</t>
         </is>
       </c>
       <c r="C12">
-        <v>34.4461125707216</v>
+        <v>54.5923388842959</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10304</t>
+          <t>10102</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Puyehue</t>
+          <t>Calbuco</t>
         </is>
       </c>
       <c r="C13">
-        <v>34.2551192327631</v>
+        <v>53.5167978816464</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10307</t>
+          <t>10302</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>San Pablo</t>
+          <t>Puerto Octay</t>
         </is>
       </c>
       <c r="C14">
-        <v>34.0208641366847</v>
+        <v>53.3922372988324</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10303</t>
+          <t>10304</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Purranque</t>
+          <t>Puyehue</t>
         </is>
       </c>
       <c r="C15">
-        <v>33.6464597059585</v>
+        <v>52.6715176715177</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="C16">
-        <v>33.5098326144999</v>
+        <v>52.3910582908885</v>
       </c>
     </row>
     <row r="17">
@@ -609,217 +609,2917 @@
         </is>
       </c>
       <c r="C17">
-        <v>32.8475543932393</v>
+        <v>52.1254343047579</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10204</t>
+          <t>10210</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Curaco de Vélez</t>
+          <t>Quinchao</t>
         </is>
       </c>
       <c r="C18">
-        <v>32.7939142461964</v>
+        <v>51.6268980477223</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10209</t>
+          <t>10109</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Quemchi</t>
+          <t>Puerto Varas</t>
         </is>
       </c>
       <c r="C19">
-        <v>31.5906348056964</v>
+        <v>51.5293414366843</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10206</t>
+          <t>10101</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Puqueldón</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="C20">
-        <v>31.4829132518942</v>
+        <v>51.5286743860368</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10401</t>
+          <t>10209</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Chaitén</t>
+          <t>Quemchi</t>
         </is>
       </c>
       <c r="C21">
-        <v>31.4563517226802</v>
+        <v>50.8512544802867</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10210</t>
+          <t>10206</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Quinchao</t>
+          <t>Puqueldón</t>
         </is>
       </c>
       <c r="C22">
-        <v>30.6235716617695</v>
+        <v>50.6870567375887</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10404</t>
+          <t>10205</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Palena</t>
+          <t>Dalcahue</t>
         </is>
       </c>
       <c r="C23">
-        <v>29.3484340044743</v>
+        <v>50.2845210127904</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>10207</t>
+          <t>10101</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Queilén</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="C24">
-        <v>29.2902311382468</v>
+        <v>50.1016866559262</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10104</t>
+          <t>10107</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Fresia</t>
+          <t>Llanquihue</t>
         </is>
       </c>
       <c r="C25">
-        <v>28.3114067263331</v>
+        <v>49.8038479195359</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>10403</t>
+          <t>10404</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Hualaihué</t>
+          <t>Palena</t>
         </is>
       </c>
       <c r="C26">
-        <v>28.1016949152542</v>
+        <v>48.937908496732</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10108</t>
+          <t>10302</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Maullín</t>
+          <t>Puerto Octay</t>
         </is>
       </c>
       <c r="C27">
-        <v>27.1507285255904</v>
+        <v>47.2731028783914</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10106</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Los Muermos</t>
+          <t>Osorno</t>
         </is>
       </c>
       <c r="C28">
-        <v>25.8144703749196</v>
+        <v>47.1827906268272</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10402</t>
+          <t>10201</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Futaleufú</t>
+          <t>Castro</t>
         </is>
       </c>
       <c r="C29">
-        <v>24.5749158249158</v>
+        <v>47.1307572796071</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10103</t>
+          <t>10401</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Cochamó</t>
+          <t>Chaitén</t>
         </is>
       </c>
       <c r="C30">
-        <v>20.8352620480379</v>
+        <v>46.8915662650602</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>10107</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Llanquihue</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>46.8871512199291</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>10109</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Puerto Varas</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>46.2842117843911</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>10302</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Puerto Octay</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>46.2233169129721</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>10301</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Osorno</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>46.0644377979804</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>10108</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Maullín</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>45.4208754208754</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>10104</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Fresia</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>45.1110079678193</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>10207</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Queilén</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>45.0065703022339</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>10105</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Frutillar</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>44.6234876929495</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>10208</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Quellón</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>44.5575773035173</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>10105</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Frutillar</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>44.0123146519226</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>10403</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Hualaihué</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>43.8750546089996</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>10101</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Puerto Montt</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>43.5613470786349</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>10305</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Río Negro</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>43.3950431466988</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>10201</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Castro</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>43.2835942198599</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>10304</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Puyehue</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>43.0178351228608</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>10106</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Los Muermos</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>42.9739814956806</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>10304</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Puyehue</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>42.7555958862674</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>10208</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Quellón</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>42.3115349682107</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>10307</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>San Pablo</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>42.2708962739174</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>10303</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Purranque</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>42.1074453592371</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>10303</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Purranque</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>42.0274211263872</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>10204</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Curaco de Vélez</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>41.9867235656709</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>10305</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Río Negro</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>41.7870014270856</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>10402</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Futaleufú</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>41.7532263141328</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>10307</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>San Pablo</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>41.5898512366524</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>10208</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Quellón</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>41.4218755721557</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>10109</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Puerto Varas</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>41.2931971397749</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>10203</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Chonchi</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>41.1398387545177</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>10102</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Calbuco</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>40.7983160607373</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>10102</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Calbuco</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>40.5211141060198</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>10206</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Puqueldón</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>40.5102148830317</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>10203</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Chonchi</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>40.5001819352311</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>10202</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Ancud</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>40.4625097538483</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>10208</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Quellón</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>40.4280291679153</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>10201</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Castro</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>39.630191473859</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>10210</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Quinchao</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>39.5178533247808</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>10107</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Llanquihue</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>38.9523256564093</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>10205</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Dalcahue</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>38.9350104821803</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>10205</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Dalcahue</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>38.5918460312037</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>10204</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Curaco de Vélez</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>38.5577372604021</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>10206</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Puqueldón</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>38.403342366757</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>10301</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Osorno</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>38.2989173475838</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>10208</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Quellón</t>
+        </is>
+      </c>
+      <c r="C73">
+        <v>38.0681732066264</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>10101</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Puerto Montt</t>
+        </is>
+      </c>
+      <c r="C74">
+        <v>37.2480692710508</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>10209</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Quemchi</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>37.1785731260992</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>10101</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Puerto Montt</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>37.0659607868968</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>10105</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Frutillar</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>36.64247477867</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>10302</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Puerto Octay</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>36.6169646432525</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>10401</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Chaitén</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>36.56117146906</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>10404</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Palena</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>36.5464111236377</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>10210</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Quinchao</t>
+        </is>
+      </c>
+      <c r="C81">
+        <v>36.3815065261834</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>10107</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Llanquihue</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>36.343896713615</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>10202</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Ancud</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>36.246621776373</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>10109</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Puerto Varas</t>
+        </is>
+      </c>
+      <c r="C84">
+        <v>36.2353245159311</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>10102</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Calbuco</t>
+        </is>
+      </c>
+      <c r="C85">
+        <v>36.2075652724192</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>10201</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Castro</t>
+        </is>
+      </c>
+      <c r="C86">
+        <v>36.1214533817274</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>10203</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Chonchi</t>
+        </is>
+      </c>
+      <c r="C87">
+        <v>36.035610664039</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>10209</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Quemchi</t>
+        </is>
+      </c>
+      <c r="C88">
+        <v>36.016016016016</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>10302</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Puerto Octay</t>
+        </is>
+      </c>
+      <c r="C89">
+        <v>35.8230134158927</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>10205</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Dalcahue</t>
+        </is>
+      </c>
+      <c r="C90">
+        <v>35.7405549983283</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>10203</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Chonchi</t>
+        </is>
+      </c>
+      <c r="C91">
+        <v>35.6121673003802</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>10401</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Chaitén</t>
+        </is>
+      </c>
+      <c r="C92">
+        <v>35.5175127902401</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>10209</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Quemchi</t>
+        </is>
+      </c>
+      <c r="C93">
+        <v>35.5129282180528</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>10206</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Puqueldón</t>
+        </is>
+      </c>
+      <c r="C94">
+        <v>35.0219423774089</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>10104</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Fresia</t>
+        </is>
+      </c>
+      <c r="C95">
+        <v>35.0219005903637</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>10102</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Calbuco</t>
+        </is>
+      </c>
+      <c r="C96">
+        <v>34.6602366386631</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>10307</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>San Pablo</t>
+        </is>
+      </c>
+      <c r="C97">
+        <v>34.5970433953267</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>10403</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Hualaihué</t>
+        </is>
+      </c>
+      <c r="C98">
+        <v>34.5534374724208</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>10205</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Dalcahue</t>
+        </is>
+      </c>
+      <c r="C99">
+        <v>34.4461125707216</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>10304</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Puyehue</t>
+        </is>
+      </c>
+      <c r="C100">
+        <v>34.2551192327631</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>10207</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Queilén</t>
+        </is>
+      </c>
+      <c r="C101">
+        <v>34.0363210310486</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>10307</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>San Pablo</t>
+        </is>
+      </c>
+      <c r="C102">
+        <v>34.0208641366847</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>10201</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Castro</t>
+        </is>
+      </c>
+      <c r="C103">
+        <v>33.9189170212467</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>10104</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Fresia</t>
+        </is>
+      </c>
+      <c r="C104">
+        <v>33.755581440497</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>10303</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Purranque</t>
+        </is>
+      </c>
+      <c r="C105">
+        <v>33.6464597059585</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>10105</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Frutillar</t>
+        </is>
+      </c>
+      <c r="C106">
+        <v>33.5344731254889</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>10305</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Río Negro</t>
+        </is>
+      </c>
+      <c r="C107">
+        <v>33.5098326144999</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>10301</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Osorno</t>
+        </is>
+      </c>
+      <c r="C108">
+        <v>33.258287483996</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>10103</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Cochamó</t>
+        </is>
+      </c>
+      <c r="C109">
+        <v>33.2529290144728</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>10303</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Purranque</t>
+        </is>
+      </c>
+      <c r="C110">
+        <v>33.0062427572801</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>10202</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Ancud</t>
+        </is>
+      </c>
+      <c r="C111">
+        <v>32.8475543932393</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>10204</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Curaco de Vélez</t>
+        </is>
+      </c>
+      <c r="C112">
+        <v>32.7939142461964</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>10207</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Queilén</t>
+        </is>
+      </c>
+      <c r="C113">
+        <v>32.7615780445969</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>10304</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Puyehue</t>
+        </is>
+      </c>
+      <c r="C114">
+        <v>32.582671957672</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>10305</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Río Negro</t>
+        </is>
+      </c>
+      <c r="C115">
+        <v>32.2511155562394</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>10108</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Maullín</t>
+        </is>
+      </c>
+      <c r="C116">
+        <v>31.7905637449147</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>10203</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Chonchi</t>
+        </is>
+      </c>
+      <c r="C117">
+        <v>31.7640127473822</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>10209</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Quemchi</t>
+        </is>
+      </c>
+      <c r="C118">
+        <v>31.5906348056964</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>10108</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Maullín</t>
+        </is>
+      </c>
+      <c r="C119">
+        <v>31.485015010431</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>10206</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Puqueldón</t>
+        </is>
+      </c>
+      <c r="C120">
+        <v>31.4829132518942</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>10401</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Chaitén</t>
+        </is>
+      </c>
+      <c r="C121">
+        <v>31.4563517226802</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>10403</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Hualaihué</t>
+        </is>
+      </c>
+      <c r="C122">
+        <v>31.3875226507895</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>10301</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Osorno</t>
+        </is>
+      </c>
+      <c r="C123">
+        <v>31.2406074064105</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>10109</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Puerto Varas</t>
+        </is>
+      </c>
+      <c r="C124">
+        <v>31.2030248535989</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>10107</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Llanquihue</t>
+        </is>
+      </c>
+      <c r="C125">
+        <v>30.9134199134199</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>10210</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Quinchao</t>
+        </is>
+      </c>
+      <c r="C126">
+        <v>30.6235716617695</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>10104</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Fresia</t>
+        </is>
+      </c>
+      <c r="C127">
+        <v>30.4955370883349</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>10404</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Palena</t>
+        </is>
+      </c>
+      <c r="C128">
+        <v>30.224429727741</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>10108</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Maullín</t>
+        </is>
+      </c>
+      <c r="C129">
+        <v>30.2134769813956</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>10205</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Dalcahue</t>
+        </is>
+      </c>
+      <c r="C130">
+        <v>30.005254134174</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>10106</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Los Muermos</t>
+        </is>
+      </c>
+      <c r="C131">
+        <v>29.9857402424159</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>10207</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Queilén</t>
+        </is>
+      </c>
+      <c r="C132">
+        <v>29.9367769706753</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>10401</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Chaitén</t>
+        </is>
+      </c>
+      <c r="C133">
+        <v>29.5809223215851</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>10202</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Ancud</t>
+        </is>
+      </c>
+      <c r="C134">
+        <v>29.5419718109086</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>10404</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Palena</t>
+        </is>
+      </c>
+      <c r="C135">
+        <v>29.3484340044743</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>10202</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Ancud</t>
+        </is>
+      </c>
+      <c r="C136">
+        <v>29.3168445900715</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>10207</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Queilén</t>
+        </is>
+      </c>
+      <c r="C137">
+        <v>29.2902311382468</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>10402</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Futaleufú</t>
+        </is>
+      </c>
+      <c r="C138">
+        <v>29.2376317923763</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>10106</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Los Muermos</t>
+        </is>
+      </c>
+      <c r="C139">
+        <v>29.1089566020314</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>10105</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Frutillar</t>
+        </is>
+      </c>
+      <c r="C140">
+        <v>28.8658536585366</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>10404</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Palena</t>
+        </is>
+      </c>
+      <c r="C141">
+        <v>28.4486016628874</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>10104</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Fresia</t>
+        </is>
+      </c>
+      <c r="C142">
+        <v>28.3114067263331</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>10102</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Calbuco</t>
+        </is>
+      </c>
+      <c r="C143">
+        <v>28.236381390807</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>10403</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Hualaihué</t>
+        </is>
+      </c>
+      <c r="C144">
+        <v>28.1016949152542</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
           <t>10306</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B145" t="inlineStr">
         <is>
           <t>San Juan de la Costa</t>
         </is>
       </c>
-      <c r="C31">
+      <c r="C145">
+        <v>28.0098746676795</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>10106</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Los Muermos</t>
+        </is>
+      </c>
+      <c r="C146">
+        <v>27.8082066730567</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>10204</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Curaco de Vélez</t>
+        </is>
+      </c>
+      <c r="C147">
+        <v>27.613194663305</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>10204</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Curaco de Vélez</t>
+        </is>
+      </c>
+      <c r="C148">
+        <v>27.3708306082407</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>10108</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Maullín</t>
+        </is>
+      </c>
+      <c r="C149">
+        <v>27.1507285255904</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>10403</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Hualaihué</t>
+        </is>
+      </c>
+      <c r="C150">
+        <v>26.8854632852644</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>10402</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Futaleufú</t>
+        </is>
+      </c>
+      <c r="C151">
+        <v>26.8559353178978</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>10401</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Chaitén</t>
+        </is>
+      </c>
+      <c r="C152">
+        <v>26.7442922374429</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>10103</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Cochamó</t>
+        </is>
+      </c>
+      <c r="C153">
+        <v>26.7310317924712</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>10404</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Palena</t>
+        </is>
+      </c>
+      <c r="C154">
+        <v>26.5471167369902</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>10210</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Quinchao</t>
+        </is>
+      </c>
+      <c r="C155">
+        <v>26.4327648867766</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>10209</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Quemchi</t>
+        </is>
+      </c>
+      <c r="C156">
+        <v>25.8251189250159</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>10106</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Los Muermos</t>
+        </is>
+      </c>
+      <c r="C157">
+        <v>25.8144703749196</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>10207</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Queilén</t>
+        </is>
+      </c>
+      <c r="C158">
+        <v>25.6987577639752</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>10303</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Purranque</t>
+        </is>
+      </c>
+      <c r="C159">
+        <v>25.6545820745217</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>10302</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Puerto Octay</t>
+        </is>
+      </c>
+      <c r="C160">
+        <v>25.3870343492985</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>10210</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Quinchao</t>
+        </is>
+      </c>
+      <c r="C161">
+        <v>25.3278372384534</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>10307</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>San Pablo</t>
+        </is>
+      </c>
+      <c r="C162">
+        <v>25.1348262437944</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>10103</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Cochamó</t>
+        </is>
+      </c>
+      <c r="C163">
+        <v>24.5791740066549</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>10402</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Futaleufú</t>
+        </is>
+      </c>
+      <c r="C164">
+        <v>24.5749158249158</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>10305</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Río Negro</t>
+        </is>
+      </c>
+      <c r="C165">
+        <v>24.1500506003665</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>10304</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Puyehue</t>
+        </is>
+      </c>
+      <c r="C166">
+        <v>24.0247199691</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>10402</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Futaleufú</t>
+        </is>
+      </c>
+      <c r="C167">
+        <v>23.5437633424825</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>10306</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>San Juan de la Costa</t>
+        </is>
+      </c>
+      <c r="C168">
+        <v>23.1914893617021</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>10206</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Puqueldón</t>
+        </is>
+      </c>
+      <c r="C169">
+        <v>22.9154108900944</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>10104</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Fresia</t>
+        </is>
+      </c>
+      <c r="C170">
+        <v>22.7829801215706</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>10103</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Cochamó</t>
+        </is>
+      </c>
+      <c r="C171">
+        <v>22.6584022038567</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>10402</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Futaleufú</t>
+        </is>
+      </c>
+      <c r="C172">
+        <v>22.6467847157502</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>10108</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Maullín</t>
+        </is>
+      </c>
+      <c r="C173">
+        <v>22.5134737873591</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>10106</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Los Muermos</t>
+        </is>
+      </c>
+      <c r="C174">
+        <v>21.4969290101414</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>10403</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Hualaihué</t>
+        </is>
+      </c>
+      <c r="C175">
+        <v>21.3289790624421</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>10103</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Cochamó</t>
+        </is>
+      </c>
+      <c r="C176">
+        <v>20.8352620480379</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>10306</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>San Juan de la Costa</t>
+        </is>
+      </c>
+      <c r="C177">
+        <v>18.2850061957869</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>10306</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>San Juan de la Costa</t>
+        </is>
+      </c>
+      <c r="C178">
+        <v>17.5548112058465</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>10103</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Cochamó</t>
+        </is>
+      </c>
+      <c r="C179">
+        <v>16.6883468834688</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>10306</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>San Juan de la Costa</t>
+        </is>
+      </c>
+      <c r="C180">
         <v>16.4464783127736</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>10306</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>San Juan de la Costa</t>
+        </is>
+      </c>
+      <c r="C181">
+        <v>14.3293378995434</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>10109</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Puerto Varas</t>
+        </is>
+      </c>
+      <c r="C182">
+        <v>11.9530326068593</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>10302</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Puerto Octay</t>
+        </is>
+      </c>
+      <c r="C183">
+        <v>11.9399382000773</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>10101</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Puerto Montt</t>
+        </is>
+      </c>
+      <c r="C184">
+        <v>11.0189482933165</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>10105</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Frutillar</t>
+        </is>
+      </c>
+      <c r="C185">
+        <v>10.5481016271767</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>10304</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Puyehue</t>
+        </is>
+      </c>
+      <c r="C186">
+        <v>9.908614519427401</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>10107</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Llanquihue</t>
+        </is>
+      </c>
+      <c r="C187">
+        <v>9.895141042682029</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>10401</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Chaitén</t>
+        </is>
+      </c>
+      <c r="C188">
+        <v>9.54241071428571</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>10305</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Río Negro</t>
+        </is>
+      </c>
+      <c r="C189">
+        <v>9.18288872867099</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>10301</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Osorno</t>
+        </is>
+      </c>
+      <c r="C190">
+        <v>9.16561179744374</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>10307</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>San Pablo</t>
+        </is>
+      </c>
+      <c r="C191">
+        <v>8.49367619732662</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>10208</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Quellón</t>
+        </is>
+      </c>
+      <c r="C192">
+        <v>8.436184462303871</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>10303</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Purranque</t>
+        </is>
+      </c>
+      <c r="C193">
+        <v>8.421583459404941</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>10404</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Palena</t>
+        </is>
+      </c>
+      <c r="C194">
+        <v>8.036036036036039</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>10201</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Castro</t>
+        </is>
+      </c>
+      <c r="C195">
+        <v>7.75902786723346</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>10202</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Ancud</t>
+        </is>
+      </c>
+      <c r="C196">
+        <v>7.44824525862901</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>10203</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Chonchi</t>
+        </is>
+      </c>
+      <c r="C197">
+        <v>6.86349693251534</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>10207</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Queilén</t>
+        </is>
+      </c>
+      <c r="C198">
+        <v>6.67447306791569</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>10204</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Curaco de Vélez</t>
+        </is>
+      </c>
+      <c r="C199">
+        <v>6.67295202178923</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>10210</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Quinchao</t>
+        </is>
+      </c>
+      <c r="C200">
+        <v>6.5950462548493</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>10104</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Fresia</t>
+        </is>
+      </c>
+      <c r="C201">
+        <v>6.48148148148148</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>10102</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Calbuco</t>
+        </is>
+      </c>
+      <c r="C202">
+        <v>6.47533855137284</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>10205</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Dalcahue</t>
+        </is>
+      </c>
+      <c r="C203">
+        <v>6.2101799341875</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>10403</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Hualaihué</t>
+        </is>
+      </c>
+      <c r="C204">
+        <v>5.81420765027322</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>10106</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Los Muermos</t>
+        </is>
+      </c>
+      <c r="C205">
+        <v>5.65024828882029</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>10108</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Maullín</t>
+        </is>
+      </c>
+      <c r="C206">
+        <v>5.55877104133507</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>10206</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Puqueldón</t>
+        </is>
+      </c>
+      <c r="C207">
+        <v>5.45977011494253</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>10209</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Quemchi</t>
+        </is>
+      </c>
+      <c r="C208">
+        <v>5.41046522512403</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>10103</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Cochamó</t>
+        </is>
+      </c>
+      <c r="C209">
+        <v>4.38737292669877</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>10402</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Futaleufú</t>
+        </is>
+      </c>
+      <c r="C210">
+        <v>3.38066260987153</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>10306</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>San Juan de la Costa</t>
+        </is>
+      </c>
+      <c r="C211">
+        <v>2.57314524555904</v>
       </c>
     </row>
   </sheetData>
